--- a/src/main/resources/doc/PONKIDS-테이블정의서_v4.4.xlsx
+++ b/src/main/resources/doc/PONKIDS-테이블정의서_v4.4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20406"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20407"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\git\ponkids\src\main\resources\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\jjeovi\ponkids\eclipse\workspace\ponkids\src\main\resources\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D923DC8A-5B0F-4779-8952-050A2123FAA1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A63E22-E6B9-41A9-AD87-93737E1AC95C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="495" windowWidth="15360" windowHeight="7155" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4882" uniqueCount="869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4878" uniqueCount="870">
   <si>
     <t>테이블명</t>
     <phoneticPr fontId="12" type="noConversion"/>
@@ -3488,6 +3488,10 @@
   </si>
   <si>
     <t>설문조사 사용자단에서 호출 할때 코드명을 기준으로 호출. 코드명은 중복 되어서는 안됨. 가능하면 10자 이내로</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>null 도 가능 -&gt; 로그인 하지 않은 사람도 설문조사를 할 수 있도록 구성. Null 인 경우는 로그인 하지 않은 사용자들…</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -37037,25 +37041,13 @@
       <c r="I353" s="95" t="s">
         <v>715</v>
       </c>
-      <c r="J353" s="73" t="s">
-        <v>72</v>
-      </c>
+      <c r="J353" s="73"/>
       <c r="K353" s="69"/>
-      <c r="L353" s="69">
-        <v>2</v>
-      </c>
-      <c r="M353" s="78" t="s">
-        <v>9</v>
-      </c>
-      <c r="N353" s="95" t="s">
-        <v>714</v>
-      </c>
-      <c r="O353" s="95" t="s">
-        <v>539</v>
-      </c>
-      <c r="P353" s="95" t="s">
-        <v>541</v>
-      </c>
+      <c r="L353" s="69"/>
+      <c r="M353" s="78"/>
+      <c r="N353" s="95"/>
+      <c r="O353" s="95"/>
+      <c r="P353" s="95"/>
       <c r="Q353" s="100" t="s">
         <v>172</v>
       </c>
@@ -37066,7 +37058,9 @@
       </c>
       <c r="U353" s="123"/>
       <c r="V353" s="123"/>
-      <c r="W353" s="104"/>
+      <c r="W353" s="104" t="s">
+        <v>869</v>
+      </c>
       <c r="X353" s="85"/>
       <c r="Y353" s="123"/>
       <c r="Z353" s="130" t="str">
@@ -37075,11 +37069,11 @@
       </c>
       <c r="AA353" s="125" t="str">
         <f t="shared" si="119"/>
-        <v>USER_SN INTEGER NOT NULL,</v>
+        <v>USER_SN INTEGER,</v>
       </c>
       <c r="AB353" s="125" t="str">
         <f t="shared" si="117"/>
-        <v>ALTER TABLE TB_QESTNAR_ANSWER ADD CONSTRAINT TB_QESTNAR_ANSWER_FKEY2 FOREIGN KEY(USER_SN) REFERENCES TB_USER(USER_SN) ON UPDATE CASCADE ON DELETE CASCADE;</v>
+        <v/>
       </c>
       <c r="AC353" s="125" t="str">
         <f t="shared" si="118"/>
@@ -37103,7 +37097,7 @@
       </c>
       <c r="AH353" s="131" t="str">
         <f t="shared" si="149"/>
-        <v>ALTER TABLE TB_QESTNAR_ANSWER ADD COLUMN USER_SN INTEGER NOT NULL;</v>
+        <v>ALTER TABLE TB_QESTNAR_ANSWER ADD COLUMN USER_SN INTEGER;</v>
       </c>
       <c r="AI353" s="125" t="str">
         <f t="shared" si="130"/>
